--- a/backtest_runs/20260410_193731/by_symbol/THALL/THALL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/THALL/THALL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-4894.769999999991</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>95440.90000000001</v>
@@ -679,7 +679,7 @@
         <v>-10232.09</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>85208.81000000001</v>
@@ -817,7 +817,7 @@
         <v>-2887.429999999994</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>90425.89000000001</v>
@@ -863,7 +863,7 @@
         <v>-449.2300000000091</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>89976.66</v>
@@ -909,7 +909,7 @@
         <v>-1700.059999999992</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>88276.60000000001</v>
@@ -955,7 +955,7 @@
         <v>-823.3100000000106</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>87453.29000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-370.7400000000046</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>93127.95000000001</v>
@@ -1093,7 +1093,7 @@
         <v>-145.2900000000008</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>92982.66</v>
@@ -1185,7 +1185,7 @@
         <v>-1568.129999999998</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>94986.66</v>
@@ -1231,7 +1231,7 @@
         <v>-3.339999999996962</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>94983.32000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-3318.290000000001</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>91665.03</v>
@@ -1415,7 +1415,7 @@
         <v>-5908.459999999999</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>93497.02000000002</v>
@@ -1461,7 +1461,7 @@
         <v>-1988.969999999995</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>91508.05000000002</v>
@@ -1553,7 +1553,7 @@
         <v>-1564.790000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>91653.34</v>
@@ -1645,7 +1645,7 @@
         <v>-1227.449999999985</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>100046.76</v>
